--- a/data/portfolio_editor.xlsx
+++ b/data/portfolio_editor.xlsx
@@ -1,27 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yazaki-my.sharepoint.com/personal/younes_daaiki_yazaki-europe_com/Documents/Documents/GitHub/portfolio/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_22B5AE1187109D21C5F7048105B7B1AD1CC08C54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3301A58A-F343-47E7-811D-FAE58BF7E27B}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="HOW TO USE"/>
-    <sheet r:id="rId2" sheetId="2" name="Profile"/>
-    <sheet r:id="rId3" sheetId="3" name="Skills"/>
-    <sheet r:id="rId4" sheetId="4" name="Experience"/>
-    <sheet r:id="rId5" sheetId="5" name="Education"/>
-    <sheet r:id="rId6" sheetId="6" name="Certifications"/>
-    <sheet r:id="rId7" sheetId="7" name="Languages"/>
-    <sheet r:id="rId8" sheetId="8" name="Projects"/>
+    <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
+    <sheet name="Profile" sheetId="2" r:id="rId2"/>
+    <sheet name="Skills" sheetId="3" r:id="rId3"/>
+    <sheet name="Experience" sheetId="4" r:id="rId4"/>
+    <sheet name="Education" sheetId="5" r:id="rId5"/>
+    <sheet name="Certifications" sheetId="6" r:id="rId6"/>
+    <sheet name="Languages" sheetId="7" r:id="rId7"/>
+    <sheet name="Projects" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -59,19 +78,10 @@
     <t>proj1</t>
   </si>
   <si>
-    <t>Executive KPI Dashboard — YAZAKI</t>
-  </si>
-  <si>
     <t>Power BI</t>
   </si>
   <si>
     <t>Power BI, DAX, SAP, Azure</t>
-  </si>
-  <si>
-    <t>End-to-end executive dashboard tracking operational KPIs across YAZAKI's manufacturing lines. Gathered requirements, designed the star-schema data model, and built a multi-page report consumed by senior leadership weekly.</t>
-  </si>
-  <si>
-    <t>sample_dashboard.png</t>
   </si>
   <si>
     <t>2025</t>
@@ -471,13 +481,27 @@
   <si>
     <t>Separate multiple tags with commas: Power BI, DAX, Python</t>
   </si>
+  <si>
+    <t>www.linkedin.com/in/younes-daaiki</t>
+  </si>
+  <si>
+    <t>https://younesdaaiki-cpu.github.io/portfolio/</t>
+  </si>
+  <si>
+    <t>Warehouse Space Calculation Dashboard</t>
+  </si>
+  <si>
+    <t>Developed a Power BI dashboard to analyze and optimize warehouse space, providing key metrics and insights for efficient inventory management.</t>
+  </si>
+  <si>
+    <t>Warehouse Space Calculation Dashboard.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,7 +511,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -505,13 +529,13 @@
     </font>
     <font>
       <sz val="13"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -523,9 +547,23 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -537,22 +575,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1a2e4a"/>
+        <fgColor rgb="FF1A2E4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8eff5"/>
+        <fgColor rgb="FFE8EFF5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0e7c7b"/>
+        <fgColor rgb="FF0E7C7B"/>
       </patternFill>
     </fill>
   </fills>
@@ -566,16 +604,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -588,116 +626,119 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFdddddd"/>
+        <color rgb="FFDDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="FFdddddd"/>
+        <color rgb="FFDDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="FFdddddd"/>
+        <color rgb="FFDDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFdddddd"/>
+        <color rgb="FFDDDDDD"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -708,10 +749,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -749,71 +790,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -841,7 +882,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -864,11 +905,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -877,13 +918,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -893,7 +934,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -902,7 +943,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -911,7 +952,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -919,10 +960,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -987,101 +1028,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="18" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="70.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="24">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="16" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="15" t="s">
+      <c r="B4" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="17" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="16" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="15" t="s">
+      <c r="B6" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="17" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="28.5">
-      <c r="A6" s="15" t="s">
+      <c r="B7" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="16" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="28.5">
-      <c r="A7" s="15" t="s">
+      <c r="B8" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="17" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="28.5">
-      <c r="A8" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B8" s="16" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="15" t="s">
+      <c r="B10" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="17" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="28.5">
-      <c r="A10" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1093,154 +1134,161 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="7" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="55.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="11" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20">
-      <c r="A2" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20">
-      <c r="A3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="5" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20">
-      <c r="A4" s="12" t="s">
+    <row r="6" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20">
-      <c r="A5" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="7" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20">
-      <c r="A6" s="12" t="s">
+      <c r="B7" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="9" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20">
-      <c r="A7" s="12" t="s">
+      <c r="B8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20">
-      <c r="A8" s="12" t="s">
+      <c r="B9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="9" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="50">
-      <c r="A9" s="12" t="s">
+      <c r="B10" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20">
-      <c r="A10" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20">
-      <c r="A11" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20">
-      <c r="A12" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="18" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{D6710341-1713-43F7-9A0E-E2DA60A00586}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="8" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="60.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A2" s="5" t="s">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1249,135 +1297,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="8" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="70.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="105" customFormat="1" s="1">
-      <c r="A2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="C3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="105" customFormat="1" s="1">
-      <c r="A3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:7" s="1" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="75" customFormat="1" s="1">
-      <c r="A4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="F4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="40" customFormat="1" s="1">
-      <c r="A5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1386,67 +1432,66 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="8" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A2" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1455,49 +1500,49 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="8" width="45.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="45" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+    <row r="2" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1505,47 +1550,46 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="8" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="25" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A2" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>51</v>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1554,26 +1598,25 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="7" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="35.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="35.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="55.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="35.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="35.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="8" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="30" customFormat="1" s="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1605,176 +1648,176 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="50" customFormat="1" s="1">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="50" customFormat="1" s="1">
-      <c r="A4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="50" customFormat="1" s="1">
-      <c r="A5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="50" customFormat="1" s="1">
-      <c r="A6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="6" t="s">
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="50" customFormat="1" s="1">
-      <c r="A7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="50" customFormat="1" s="1">
-      <c r="A8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>35</v>
+      <c r="J8" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio_editor.xlsx
+++ b/data/portfolio_editor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yazaki-my.sharepoint.com/personal/younes_daaiki_yazaki-europe_com/Documents/Documents/GitHub/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_22B5AE1187109D21C5F7048105B7B1AD1CC08C54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3301A58A-F343-47E7-811D-FAE58BF7E27B}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_22B5AE1187109D21C5F7048105B7B1AD1CC08C54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0287AE82-283C-49B7-9427-66B6DC25B0C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="148">
   <si>
     <t>id</t>
   </si>
@@ -93,79 +93,40 @@
     <t>proj2</t>
   </si>
   <si>
-    <t>Vendor Validation Automation — REST API Integration</t>
-  </si>
-  <si>
     <t>Python</t>
   </si>
   <si>
-    <t>Python, REST API, VIES, D&amp;B, IBAN</t>
-  </si>
-  <si>
-    <t>Python-powered automation connecting VIES (EU VAT validation), Dun &amp; Bradstreet, and IBAN.com APIs to automatically validate new vendors before SAP activation. Eliminated manual checks and reduced processing time by over 70%.</t>
-  </si>
-  <si>
     <t>proj3</t>
   </si>
   <si>
-    <t>SAP MDG Data Quality Tool</t>
-  </si>
-  <si>
     <t>Analytics</t>
   </si>
   <si>
     <t>Python, SAP, Azure, SQL, Data Quality</t>
   </si>
   <si>
-    <t>Cross-system discrepancy detection engine querying SAP tables via Azure. Surfaced mismatches in master data records at scale, enabling proactive governance before issues propagated downstream.</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
     <t>proj4</t>
   </si>
   <si>
-    <t>Power Apps Approval Workflow</t>
-  </si>
-  <si>
     <t>Power Platform</t>
   </si>
   <si>
     <t>Power Apps, Power Automate, SharePoint</t>
   </si>
   <si>
-    <t>Canvas app MVP built for top management to digitize approval workflows and replace paper-based forms. Integrated with Power Automate for automated notifications and Power BI for audit tracking.</t>
-  </si>
-  <si>
     <t>FALSE</t>
   </si>
   <si>
     <t>proj5</t>
   </si>
   <si>
-    <t>MDG Master Data Health Reports</t>
-  </si>
-  <si>
-    <t>Power BI, SAP MDG, Data Governance</t>
-  </si>
-  <si>
-    <t>Power BI suite monitoring vendor and customer master data KPIs — completeness, duplication rate, IBAN validity, tax number accuracy — surfaced to data governance stakeholders in real time.</t>
-  </si>
-  <si>
     <t>proj6</t>
   </si>
   <si>
-    <t>DCIX Factory Startup Integration — APTIV</t>
-  </si>
-  <si>
-    <t>ERP</t>
-  </si>
-  <si>
     <t>SAP MM/SD, DCIX, EDI, IDoc</t>
-  </si>
-  <si>
-    <t>Led DCIX system integration and master data setup from zero for a new APTIV factory. Configured EDI/IDoc processes and delivered training to 30+ end users across logistics and procurement teams.</t>
   </si>
   <si>
     <t>2023</t>
@@ -495,6 +456,51 @@
   </si>
   <si>
     <t>Warehouse Space Calculation Dashboard.png</t>
+  </si>
+  <si>
+    <t>Enterprise Cost Improvement Dashboard.png</t>
+  </si>
+  <si>
+    <t>Created a comprehensive Power BI dashboard to track enterprise costs, enabling management to identify trends and make data-driven decisions for cost reduction.</t>
+  </si>
+  <si>
+    <t>PBI</t>
+  </si>
+  <si>
+    <t>Vendor Master Data Accuracy Project</t>
+  </si>
+  <si>
+    <t>Led a project focused on ensuring the accuracy and integrity of vendor master data, streamlining vendor management and improving data quality across the organization.</t>
+  </si>
+  <si>
+    <t>Vendor Master Data Accuracy.png</t>
+  </si>
+  <si>
+    <t>Premium Freight Approval App.png</t>
+  </si>
+  <si>
+    <t>Premium Freight Approval App</t>
+  </si>
+  <si>
+    <t>Designed and built a custom Power Apps application to automate and manage the approval workflow for premium freight requests, reducing lead times and ensuring proper authorization.</t>
+  </si>
+  <si>
+    <t>Stock Adjustment Approval App</t>
+  </si>
+  <si>
+    <t>Developed a Power Apps solution for managing stock adjustments, providing a clear approval process to maintain accurate inventory records and reduce discrepancies.</t>
+  </si>
+  <si>
+    <t>Stock Adjustment Approval App.png</t>
+  </si>
+  <si>
+    <t>Daily Inventory Dashboard.png</t>
+  </si>
+  <si>
+    <t>Daily Inventory Dashboard</t>
+  </si>
+  <si>
+    <t>Implemented a daily inventory dashboard using Power BI, providing real-time visibility into stock levels, movement, and critical inventory metrics for operational teams.</t>
   </si>
 </sst>
 </file>
@@ -710,22 +716,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1040,89 +1046,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="14"/>
+      <c r="A1" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1147,18 +1153,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1166,77 +1172,77 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>141</v>
+        <v>104</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:2" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>142</v>
+        <v>106</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1261,34 +1267,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1316,114 +1322,114 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="1" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1446,25 +1452,25 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
@@ -1472,26 +1478,26 @@
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1514,10 +1520,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -1525,21 +1531,21 @@
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1562,34 +1568,34 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1667,7 +1673,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>12</v>
@@ -1676,10 +1682,10 @@
         <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -1695,18 +1701,20 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4"/>
+        <v>134</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
@@ -1718,25 +1726,27 @@
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>15</v>
@@ -1744,80 +1754,86 @@
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4"/>
+        <v>141</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>142</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio_editor.xlsx
+++ b/data/portfolio_editor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yazaki-my.sharepoint.com/personal/younes_daaiki_yazaki-europe_com/Documents/Documents/GitHub/portfolio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_22B5AE1187109D21C5F7048105B7B1AD1CC08C54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0287AE82-283C-49B7-9427-66B6DC25B0C5}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_22B5AE1187109D21C5F7048105B7B1AD1CC08C54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE2B8AEA-F2D9-478A-A3A6-7441CF13ACC9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="149">
   <si>
     <t>id</t>
   </si>
@@ -502,12 +502,15 @@
   <si>
     <t>Implemented a daily inventory dashboard using Power BI, providing real-time visibility into stock levels, movement, and critical inventory metrics for operational teams.</t>
   </si>
+  <si>
+    <t>proj7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,6 +570,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1608,7 +1617,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -1836,10 +1845,39 @@
         <v>25</v>
       </c>
     </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>